--- a/output/Jiangsu/镇江市_api_news.xlsx
+++ b/output/Jiangsu/镇江市_api_news.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -565,11 +565,9 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>188</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
         <v>0</v>
       </c>
@@ -613,7 +611,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -635,11 +633,9 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>114</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
         <v>0</v>
       </c>
@@ -683,7 +679,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -705,11 +701,9 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>57</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
         <v>0</v>
       </c>
@@ -753,7 +747,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -775,11 +769,9 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>53</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
         <v>0</v>
       </c>
@@ -823,7 +815,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -845,11 +837,9 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>44</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
         <v>0</v>
       </c>
@@ -893,7 +883,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -915,11 +905,9 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>31</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
         <v>0</v>
       </c>
@@ -987,9 +975,7 @@
       <c r="L8" t="n">
         <v>28</v>
       </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
         <v>0</v>
       </c>
@@ -1033,7 +1019,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1055,11 +1041,9 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>25</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
         <v>0</v>
       </c>
@@ -1127,9 +1111,7 @@
       <c r="L10" t="n">
         <v>25</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
         <v>0</v>
       </c>
@@ -1197,9 +1179,7 @@
       <c r="L11" t="n">
         <v>20</v>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
         <v>0</v>
       </c>
@@ -1243,7 +1223,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1265,11 +1245,9 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>18</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
         <v>0</v>
       </c>
@@ -1333,9 +1311,7 @@
       <c r="L13" t="n">
         <v>17</v>
       </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
         <v>0</v>
       </c>
@@ -1403,9 +1379,7 @@
       <c r="L14" t="n">
         <v>13</v>
       </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
         <v>0</v>
       </c>
@@ -1473,9 +1447,7 @@
       <c r="L15" t="n">
         <v>8</v>
       </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
         <v>0</v>
       </c>
@@ -1543,9 +1515,7 @@
       <c r="L16" t="n">
         <v>8</v>
       </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
         <v>0</v>
       </c>
@@ -1609,9 +1579,7 @@
       <c r="L17" t="n">
         <v>8</v>
       </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
         <v>0</v>
       </c>
@@ -1679,9 +1647,7 @@
       <c r="L18" t="n">
         <v>6</v>
       </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
         <v>0</v>
       </c>
